--- a/data/trans_camb/IQ2601_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-21,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-16,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-27,69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-24,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-21,52</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-16,52</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,53</t>
+          <t>-4,02</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,79</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -17,26</t>
+          <t>-31,45; -10,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -13,42</t>
+          <t>-26,39; -6,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 15,49</t>
+          <t>-10,55; 21,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,83; -11,58</t>
+          <t>-38,05; -17,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,07; -6,19</t>
+          <t>-34,63; -14,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 18,31</t>
+          <t>-28,51; 13,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,85; -17,85</t>
+          <t>-32,44; -17,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,1; -13,58</t>
+          <t>-27,56; -13,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 13,47</t>
+          <t>-12,99; 14,09</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-28,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-21,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-36,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-31,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-28,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,6%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>-5,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -24,49</t>
+          <t>-40,15; -15,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -19,45</t>
+          <t>-33,18; -9,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 20,51</t>
+          <t>-13,62; 29,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -16,06</t>
+          <t>-47,48; -23,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,13; -8,5</t>
+          <t>-43,26; -19,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 24,95</t>
+          <t>-37,97; 18,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,48; -24,26</t>
+          <t>-41,31; -24,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,21; -18,47</t>
+          <t>-34,78; -18,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 18,33</t>
+          <t>-16,6; 18,81</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-18,73</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-9,6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-6,77</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-14,16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-8,64</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-18,73</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-9,6</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>-2,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,52</t>
+          <t>-4,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,03; -7,09</t>
+          <t>-24,49; -11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -1,85</t>
+          <t>-15,85; -2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 11,84</t>
+          <t>-20,26; 4,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,58; -12,4</t>
+          <t>-20,42; -6,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -3,04</t>
+          <t>-15,73; -1,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 3,82</t>
+          <t>-15,25; 9,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -12,05</t>
+          <t>-21,26; -11,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -4,44</t>
+          <t>-13,72; -4,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 4,94</t>
+          <t>-14,77; 4,07</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-25,13%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-12,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-9,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-19,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-11,68%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-25,13%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,88%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,81%</t>
+          <t>-2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,74%</t>
+          <t>-6,38%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,42; -10,03</t>
+          <t>-31,94; -16,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -2,64</t>
+          <t>-20,45; -3,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 16,51</t>
+          <t>-26,85; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,41; -17,43</t>
+          <t>-26,83; -9,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -4,31</t>
+          <t>-20,63; -2,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 5,16</t>
+          <t>-20,68; 12,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,64; -16,78</t>
+          <t>-27,79; -16,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -6,13</t>
+          <t>-17,99; -5,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 6,63</t>
+          <t>-19,78; 5,61</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-14,75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-19,86</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-14,75</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>5,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,03; -10,6</t>
+          <t>-24,0; -6,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 8,94</t>
+          <t>-9,03; 7,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 17,72</t>
+          <t>-5,33; 20,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,07; -4,94</t>
+          <t>-28,87; -11,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 8,38</t>
+          <t>-8,27; 8,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 19,5</t>
+          <t>-13,07; 16,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,58; -10,46</t>
+          <t>-24,38; -10,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 5,85</t>
+          <t>-5,75; 6,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,28</t>
+          <t>-4,26; 14,43</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-22,06%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-29,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-22,06%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-40,14; -16,73</t>
+          <t>-33,79; -10,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 13,86</t>
+          <t>-12,74; 12,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 27,49</t>
+          <t>-7,39; 32,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,81; -8,23</t>
+          <t>-39,81; -17,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 13,28</t>
+          <t>-11,18; 13,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 30,41</t>
+          <t>-18,41; 24,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,91; -16,02</t>
+          <t>-34,55; -16,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,1</t>
+          <t>-8,17; 9,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 23,56</t>
+          <t>-5,98; 22,61</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-15,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26,22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-6,59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>10,35</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-15,02</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,14</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,46</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,55</t>
+          <t>17,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 2,17</t>
+          <t>-22,4; -6,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 18,12</t>
+          <t>7,61; 24,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 19,96</t>
+          <t>13,4; 37,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,33; -7,27</t>
+          <t>-14,66; 1,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,82; 23,54</t>
+          <t>1,97; 19,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 35,58</t>
+          <t>-5,16; 20,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -5,56</t>
+          <t>-17,05; -4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 18,9</t>
+          <t>7,08; 18,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,65; 26,14</t>
+          <t>9,29; 26,27</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-31,7%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>34,08%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-11,81%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-31,7%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>34,08%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 4,98</t>
+          <t>-44,44; -16,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 35,19</t>
+          <t>14,79; 57,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 37,52</t>
+          <t>27,18; 85,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -16,91</t>
+          <t>-24,7; 3,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,11; 54,58</t>
+          <t>3,54; 36,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,25; 80,49</t>
+          <t>-8,05; 38,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,65; -11,12</t>
+          <t>-31,78; -9,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,82; 38,59</t>
+          <t>13,18; 38,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,74; 51,54</t>
+          <t>17,5; 54,01</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-16,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7,99</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-15,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,8</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-16,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>4,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -11,26</t>
+          <t>-20,58; -12,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,15</t>
+          <t>-5,01; 3,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,7</t>
+          <t>0,87; 14,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -12,2</t>
+          <t>-19,6; -11,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,84</t>
+          <t>-8,2; 0,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 14,08</t>
+          <t>-6,94; 7,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -12,95</t>
+          <t>-18,82; -12,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,65</t>
+          <t>-5,35; 0,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,47</t>
+          <t>-0,49; 9,43</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-24,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-1,61%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-22,63%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-5,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-24,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-1,61%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -16,81</t>
+          <t>-30,86; -19,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,22</t>
+          <t>-7,59; 4,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 12,95</t>
+          <t>1,61; 22,9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -19,09</t>
+          <t>-28,01; -17,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,52</t>
+          <t>-11,64; 0,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,18; 22,01</t>
+          <t>-10,14; 10,71</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -19,71</t>
+          <t>-27,66; -19,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,99</t>
+          <t>-7,92; 0,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,3</t>
+          <t>-0,72; 14,41</t>
         </is>
       </c>
     </row>
